--- a/painel/assets/modelos/funcionarios.xlsx
+++ b/painel/assets/modelos/funcionarios.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Funcionários" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruções" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,41 +31,57 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF1B2A4A"/>
+      <color rgb="00E0A53D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="17"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C7D2E5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00A96C2A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="006B7686"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001E2738"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A2D4F"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF555555"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF721C24"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF777777"/>
-      <sz val="10"/>
+      <color rgb="001A2D4F"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,37 +90,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EDF5"/>
+        <fgColor rgb="001A2D4F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
+        <fgColor rgb="00F6E7CF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAFAFA"/>
+        <fgColor rgb="00F4F6FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B2A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF155724"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9C4"/>
+        <fgColor rgb="00FFF7D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,49 +119,117 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00E4E8EF"/>
       </left>
       <right style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00E4E8EF"/>
       </right>
       <top style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00E4E8EF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
+        <color rgb="00E4E8EF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="001F7A6E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DCEFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00B23A2C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F7DAD6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="006B7686"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00ECEEF2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00A96C2A"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F6E7CF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -228,6 +300,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Gravitas</author>
+  </authors>
+  <commentList>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>Nome completo do funcionário.</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>CPF só números, 11 dígitos (ex.: 12345678901).</t>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>Empresa empregadora.</t>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0">
+      <text>
+        <t>Cargo/função na obra.</t>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0" shapeId="0">
+      <text>
+        <t>Salário base mensal (R$).</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>ASO: status do documento. Atestado de Saúde Ocupacional. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do ASO (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="H6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-06: status do documento. EPI. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-06 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="J6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-10: status do documento. Eletricidade. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-10 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="L6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-11: status do documento. Cargas. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="M6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-11 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="N6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-12: status do documento. Máquinas. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="O6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-12 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="P6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-18: status do documento. Construção civil. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="Q6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-18 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="R6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-20: status do documento. Inflamáveis. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="S6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-20 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="T6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-23: status do documento. Incêndio. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="U6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-23 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="V6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-33: status do documento. Espaço confinado. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="W6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-33 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="X6" authorId="0" shapeId="0">
+      <text>
+        <t>NR-35: status do documento. Altura. Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="Y6" authorId="0" shapeId="0">
+      <text>
+        <t>Validade do NR-35 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+      </text>
+    </comment>
+    <comment ref="Z6" authorId="0" shapeId="0">
+      <text>
+        <t>Integração junto à CORSAN: Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+    <comment ref="AA6" authorId="0" shapeId="0">
+      <text>
+        <t>Situação no SERTRAS: Apto / Inapto / Não se aplica.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="666750" cy="666750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="419100" cy="419100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,281 +796,3116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:AA86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MODELO — IMPORTAÇÃO DE FUNCIONÁRIOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Preencha a partir da linha 7. Não altere as 6 primeiras linhas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>🟢 Colunas com fundo verde são OBRIGATÓRIAS  |  Demais colunas são opcionais  |  ⚠️ Não altere as 6 primeiras linhas</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>CPF: apenas números, 11 dígitos (ex: 12345678901).  Status docs: "Apto" ou deixe em branco.  Datas: dd/mm/aaaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="8" customHeight="1">
-      <c r="A5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>GRAVITAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>PAINEL DE CONTROLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Funcionários  ·  Modelo de Importação</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>⚠  NÃO altere as linhas 1 a 6. Cabeçalho na linha 6. Preencha a partir da LINHA 7, somente as células em amarelo claro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Listas (▾): escolha o valor. Datas DD/MM/AAAA. Decimais com vírgula. Ano = inteiro. CPF só números. Passe o mouse no título (▾) para ajuda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Nome Completo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>CPF (somente números)</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Função</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Salário</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ASO</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Validade ASO</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>NR-06</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-06</t>
         </is>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>NR-10</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-10</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>NR-11</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-11</t>
         </is>
       </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>NR-12</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-12</t>
         </is>
       </c>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>NR-18</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-18</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>NR-20</t>
         </is>
       </c>
-      <c r="S6" s="6" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-20</t>
         </is>
       </c>
-      <c r="T6" s="6" t="inlineStr">
+      <c r="T6" s="7" t="inlineStr">
         <is>
           <t>NR-23</t>
         </is>
       </c>
-      <c r="U6" s="6" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-23</t>
         </is>
       </c>
-      <c r="V6" s="6" t="inlineStr">
+      <c r="V6" s="7" t="inlineStr">
         <is>
           <t>NR-33</t>
         </is>
       </c>
-      <c r="W6" s="6" t="inlineStr">
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-33</t>
         </is>
       </c>
-      <c r="X6" s="6" t="inlineStr">
+      <c r="X6" s="7" t="inlineStr">
         <is>
           <t>NR-35</t>
         </is>
       </c>
-      <c r="Y6" s="6" t="inlineStr">
+      <c r="Y6" s="7" t="inlineStr">
         <is>
           <t>Validade NR-35</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>João da Silva</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>12345678901</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Gravitas Saneamento</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Desobstrutor</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>3200.00</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Apto</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>31/12/2025</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Apto</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>31/12/2025</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>Apto</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="inlineStr">
-        <is>
-          <t>30/06/2025</t>
-        </is>
-      </c>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="7" t="inlineStr"/>
-      <c r="T7" s="7" t="inlineStr"/>
-      <c r="U7" s="7" t="inlineStr"/>
-      <c r="V7" s="7" t="inlineStr"/>
-      <c r="W7" s="7" t="inlineStr"/>
-      <c r="X7" s="7" t="inlineStr">
-        <is>
-          <t>Apto</t>
-        </is>
-      </c>
-      <c r="Y7" s="7" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
-        </is>
-      </c>
+      <c r="Z6" s="7" t="inlineStr">
+        <is>
+          <t>Integração CORSAN</t>
+        </is>
+      </c>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>SERTRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="8" t="n"/>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="11" t="n"/>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="11" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" s="11" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="11" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="11" t="n"/>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="11" t="n"/>
+      <c r="P8" s="8" t="n"/>
+      <c r="Q8" s="11" t="n"/>
+      <c r="R8" s="8" t="n"/>
+      <c r="S8" s="11" t="n"/>
+      <c r="T8" s="8" t="n"/>
+      <c r="U8" s="11" t="n"/>
+      <c r="V8" s="8" t="n"/>
+      <c r="W8" s="11" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="11" t="n"/>
+      <c r="Z8" s="8" t="n"/>
+      <c r="AA8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="8" t="n"/>
+      <c r="S9" s="11" t="n"/>
+      <c r="T9" s="8" t="n"/>
+      <c r="U9" s="11" t="n"/>
+      <c r="V9" s="8" t="n"/>
+      <c r="W9" s="11" t="n"/>
+      <c r="X9" s="8" t="n"/>
+      <c r="Y9" s="11" t="n"/>
+      <c r="Z9" s="8" t="n"/>
+      <c r="AA9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="8" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="8" t="n"/>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="8" t="n"/>
+      <c r="O10" s="11" t="n"/>
+      <c r="P10" s="8" t="n"/>
+      <c r="Q10" s="11" t="n"/>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="11" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" s="11" t="n"/>
+      <c r="V10" s="8" t="n"/>
+      <c r="W10" s="11" t="n"/>
+      <c r="X10" s="8" t="n"/>
+      <c r="Y10" s="11" t="n"/>
+      <c r="Z10" s="8" t="n"/>
+      <c r="AA10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="11" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="11" t="n"/>
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="11" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" s="11" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="11" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="11" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="8" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="8" t="n"/>
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="8" t="n"/>
+      <c r="O12" s="11" t="n"/>
+      <c r="P12" s="8" t="n"/>
+      <c r="Q12" s="11" t="n"/>
+      <c r="R12" s="8" t="n"/>
+      <c r="S12" s="11" t="n"/>
+      <c r="T12" s="8" t="n"/>
+      <c r="U12" s="11" t="n"/>
+      <c r="V12" s="8" t="n"/>
+      <c r="W12" s="11" t="n"/>
+      <c r="X12" s="8" t="n"/>
+      <c r="Y12" s="11" t="n"/>
+      <c r="Z12" s="8" t="n"/>
+      <c r="AA12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="11" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="11" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="11" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="11" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="11" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="11" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="8" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="11" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="11" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="11" t="n"/>
+      <c r="T14" s="8" t="n"/>
+      <c r="U14" s="11" t="n"/>
+      <c r="V14" s="8" t="n"/>
+      <c r="W14" s="11" t="n"/>
+      <c r="X14" s="8" t="n"/>
+      <c r="Y14" s="11" t="n"/>
+      <c r="Z14" s="8" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="8" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="11" t="n"/>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="11" t="n"/>
+      <c r="R15" s="8" t="n"/>
+      <c r="S15" s="11" t="n"/>
+      <c r="T15" s="8" t="n"/>
+      <c r="U15" s="11" t="n"/>
+      <c r="V15" s="8" t="n"/>
+      <c r="W15" s="11" t="n"/>
+      <c r="X15" s="8" t="n"/>
+      <c r="Y15" s="11" t="n"/>
+      <c r="Z15" s="8" t="n"/>
+      <c r="AA15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="11" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="11" t="n"/>
+      <c r="R16" s="8" t="n"/>
+      <c r="S16" s="11" t="n"/>
+      <c r="T16" s="8" t="n"/>
+      <c r="U16" s="11" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="11" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="11" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="8" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="8" t="n"/>
+      <c r="M17" s="11" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="11" t="n"/>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="11" t="n"/>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="11" t="n"/>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="11" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="11" t="n"/>
+      <c r="X17" s="8" t="n"/>
+      <c r="Y17" s="11" t="n"/>
+      <c r="Z17" s="8" t="n"/>
+      <c r="AA17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="11" t="n"/>
+      <c r="P18" s="8" t="n"/>
+      <c r="Q18" s="11" t="n"/>
+      <c r="R18" s="8" t="n"/>
+      <c r="S18" s="11" t="n"/>
+      <c r="T18" s="8" t="n"/>
+      <c r="U18" s="11" t="n"/>
+      <c r="V18" s="8" t="n"/>
+      <c r="W18" s="11" t="n"/>
+      <c r="X18" s="8" t="n"/>
+      <c r="Y18" s="11" t="n"/>
+      <c r="Z18" s="8" t="n"/>
+      <c r="AA18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="8" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="11" t="n"/>
+      <c r="P19" s="8" t="n"/>
+      <c r="Q19" s="11" t="n"/>
+      <c r="R19" s="8" t="n"/>
+      <c r="S19" s="11" t="n"/>
+      <c r="T19" s="8" t="n"/>
+      <c r="U19" s="11" t="n"/>
+      <c r="V19" s="8" t="n"/>
+      <c r="W19" s="11" t="n"/>
+      <c r="X19" s="8" t="n"/>
+      <c r="Y19" s="11" t="n"/>
+      <c r="Z19" s="8" t="n"/>
+      <c r="AA19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="11" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="11" t="n"/>
+      <c r="P20" s="8" t="n"/>
+      <c r="Q20" s="11" t="n"/>
+      <c r="R20" s="8" t="n"/>
+      <c r="S20" s="11" t="n"/>
+      <c r="T20" s="8" t="n"/>
+      <c r="U20" s="11" t="n"/>
+      <c r="V20" s="8" t="n"/>
+      <c r="W20" s="11" t="n"/>
+      <c r="X20" s="8" t="n"/>
+      <c r="Y20" s="11" t="n"/>
+      <c r="Z20" s="8" t="n"/>
+      <c r="AA20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="11" t="n"/>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="11" t="n"/>
+      <c r="R21" s="8" t="n"/>
+      <c r="S21" s="11" t="n"/>
+      <c r="T21" s="8" t="n"/>
+      <c r="U21" s="11" t="n"/>
+      <c r="V21" s="8" t="n"/>
+      <c r="W21" s="11" t="n"/>
+      <c r="X21" s="8" t="n"/>
+      <c r="Y21" s="11" t="n"/>
+      <c r="Z21" s="8" t="n"/>
+      <c r="AA21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="11" t="n"/>
+      <c r="P22" s="8" t="n"/>
+      <c r="Q22" s="11" t="n"/>
+      <c r="R22" s="8" t="n"/>
+      <c r="S22" s="11" t="n"/>
+      <c r="T22" s="8" t="n"/>
+      <c r="U22" s="11" t="n"/>
+      <c r="V22" s="8" t="n"/>
+      <c r="W22" s="11" t="n"/>
+      <c r="X22" s="8" t="n"/>
+      <c r="Y22" s="11" t="n"/>
+      <c r="Z22" s="8" t="n"/>
+      <c r="AA22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="11" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="11" t="n"/>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="11" t="n"/>
+      <c r="R23" s="8" t="n"/>
+      <c r="S23" s="11" t="n"/>
+      <c r="T23" s="8" t="n"/>
+      <c r="U23" s="11" t="n"/>
+      <c r="V23" s="8" t="n"/>
+      <c r="W23" s="11" t="n"/>
+      <c r="X23" s="8" t="n"/>
+      <c r="Y23" s="11" t="n"/>
+      <c r="Z23" s="8" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="11" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="11" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="11" t="n"/>
+      <c r="R24" s="8" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="8" t="n"/>
+      <c r="U24" s="11" t="n"/>
+      <c r="V24" s="8" t="n"/>
+      <c r="W24" s="11" t="n"/>
+      <c r="X24" s="8" t="n"/>
+      <c r="Y24" s="11" t="n"/>
+      <c r="Z24" s="8" t="n"/>
+      <c r="AA24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="8" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="11" t="n"/>
+      <c r="P25" s="8" t="n"/>
+      <c r="Q25" s="11" t="n"/>
+      <c r="R25" s="8" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="8" t="n"/>
+      <c r="U25" s="11" t="n"/>
+      <c r="V25" s="8" t="n"/>
+      <c r="W25" s="11" t="n"/>
+      <c r="X25" s="8" t="n"/>
+      <c r="Y25" s="11" t="n"/>
+      <c r="Z25" s="8" t="n"/>
+      <c r="AA25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="11" t="n"/>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="11" t="n"/>
+      <c r="P26" s="8" t="n"/>
+      <c r="Q26" s="11" t="n"/>
+      <c r="R26" s="8" t="n"/>
+      <c r="S26" s="11" t="n"/>
+      <c r="T26" s="8" t="n"/>
+      <c r="U26" s="11" t="n"/>
+      <c r="V26" s="8" t="n"/>
+      <c r="W26" s="11" t="n"/>
+      <c r="X26" s="8" t="n"/>
+      <c r="Y26" s="11" t="n"/>
+      <c r="Z26" s="8" t="n"/>
+      <c r="AA26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="8" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="8" t="n"/>
+      <c r="O27" s="11" t="n"/>
+      <c r="P27" s="8" t="n"/>
+      <c r="Q27" s="11" t="n"/>
+      <c r="R27" s="8" t="n"/>
+      <c r="S27" s="11" t="n"/>
+      <c r="T27" s="8" t="n"/>
+      <c r="U27" s="11" t="n"/>
+      <c r="V27" s="8" t="n"/>
+      <c r="W27" s="11" t="n"/>
+      <c r="X27" s="8" t="n"/>
+      <c r="Y27" s="11" t="n"/>
+      <c r="Z27" s="8" t="n"/>
+      <c r="AA27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="8" t="n"/>
+      <c r="O28" s="11" t="n"/>
+      <c r="P28" s="8" t="n"/>
+      <c r="Q28" s="11" t="n"/>
+      <c r="R28" s="8" t="n"/>
+      <c r="S28" s="11" t="n"/>
+      <c r="T28" s="8" t="n"/>
+      <c r="U28" s="11" t="n"/>
+      <c r="V28" s="8" t="n"/>
+      <c r="W28" s="11" t="n"/>
+      <c r="X28" s="8" t="n"/>
+      <c r="Y28" s="11" t="n"/>
+      <c r="Z28" s="8" t="n"/>
+      <c r="AA28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="8" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="11" t="n"/>
+      <c r="P29" s="8" t="n"/>
+      <c r="Q29" s="11" t="n"/>
+      <c r="R29" s="8" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="8" t="n"/>
+      <c r="U29" s="11" t="n"/>
+      <c r="V29" s="8" t="n"/>
+      <c r="W29" s="11" t="n"/>
+      <c r="X29" s="8" t="n"/>
+      <c r="Y29" s="11" t="n"/>
+      <c r="Z29" s="8" t="n"/>
+      <c r="AA29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="8" t="n"/>
+      <c r="O30" s="11" t="n"/>
+      <c r="P30" s="8" t="n"/>
+      <c r="Q30" s="11" t="n"/>
+      <c r="R30" s="8" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="8" t="n"/>
+      <c r="U30" s="11" t="n"/>
+      <c r="V30" s="8" t="n"/>
+      <c r="W30" s="11" t="n"/>
+      <c r="X30" s="8" t="n"/>
+      <c r="Y30" s="11" t="n"/>
+      <c r="Z30" s="8" t="n"/>
+      <c r="AA30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="8" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="8" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="8" t="n"/>
+      <c r="O31" s="11" t="n"/>
+      <c r="P31" s="8" t="n"/>
+      <c r="Q31" s="11" t="n"/>
+      <c r="R31" s="8" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="8" t="n"/>
+      <c r="U31" s="11" t="n"/>
+      <c r="V31" s="8" t="n"/>
+      <c r="W31" s="11" t="n"/>
+      <c r="X31" s="8" t="n"/>
+      <c r="Y31" s="11" t="n"/>
+      <c r="Z31" s="8" t="n"/>
+      <c r="AA31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="8" t="n"/>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="8" t="n"/>
+      <c r="O32" s="11" t="n"/>
+      <c r="P32" s="8" t="n"/>
+      <c r="Q32" s="11" t="n"/>
+      <c r="R32" s="8" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="8" t="n"/>
+      <c r="U32" s="11" t="n"/>
+      <c r="V32" s="8" t="n"/>
+      <c r="W32" s="11" t="n"/>
+      <c r="X32" s="8" t="n"/>
+      <c r="Y32" s="11" t="n"/>
+      <c r="Z32" s="8" t="n"/>
+      <c r="AA32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="8" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="8" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="8" t="n"/>
+      <c r="O33" s="11" t="n"/>
+      <c r="P33" s="8" t="n"/>
+      <c r="Q33" s="11" t="n"/>
+      <c r="R33" s="8" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="8" t="n"/>
+      <c r="U33" s="11" t="n"/>
+      <c r="V33" s="8" t="n"/>
+      <c r="W33" s="11" t="n"/>
+      <c r="X33" s="8" t="n"/>
+      <c r="Y33" s="11" t="n"/>
+      <c r="Z33" s="8" t="n"/>
+      <c r="AA33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="11" t="n"/>
+      <c r="N34" s="8" t="n"/>
+      <c r="O34" s="11" t="n"/>
+      <c r="P34" s="8" t="n"/>
+      <c r="Q34" s="11" t="n"/>
+      <c r="R34" s="8" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="8" t="n"/>
+      <c r="U34" s="11" t="n"/>
+      <c r="V34" s="8" t="n"/>
+      <c r="W34" s="11" t="n"/>
+      <c r="X34" s="8" t="n"/>
+      <c r="Y34" s="11" t="n"/>
+      <c r="Z34" s="8" t="n"/>
+      <c r="AA34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="11" t="n"/>
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="11" t="n"/>
+      <c r="P35" s="8" t="n"/>
+      <c r="Q35" s="11" t="n"/>
+      <c r="R35" s="8" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="8" t="n"/>
+      <c r="U35" s="11" t="n"/>
+      <c r="V35" s="8" t="n"/>
+      <c r="W35" s="11" t="n"/>
+      <c r="X35" s="8" t="n"/>
+      <c r="Y35" s="11" t="n"/>
+      <c r="Z35" s="8" t="n"/>
+      <c r="AA35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="11" t="n"/>
+      <c r="N36" s="8" t="n"/>
+      <c r="O36" s="11" t="n"/>
+      <c r="P36" s="8" t="n"/>
+      <c r="Q36" s="11" t="n"/>
+      <c r="R36" s="8" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="8" t="n"/>
+      <c r="U36" s="11" t="n"/>
+      <c r="V36" s="8" t="n"/>
+      <c r="W36" s="11" t="n"/>
+      <c r="X36" s="8" t="n"/>
+      <c r="Y36" s="11" t="n"/>
+      <c r="Z36" s="8" t="n"/>
+      <c r="AA36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="8" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="11" t="n"/>
+      <c r="N37" s="8" t="n"/>
+      <c r="O37" s="11" t="n"/>
+      <c r="P37" s="8" t="n"/>
+      <c r="Q37" s="11" t="n"/>
+      <c r="R37" s="8" t="n"/>
+      <c r="S37" s="11" t="n"/>
+      <c r="T37" s="8" t="n"/>
+      <c r="U37" s="11" t="n"/>
+      <c r="V37" s="8" t="n"/>
+      <c r="W37" s="11" t="n"/>
+      <c r="X37" s="8" t="n"/>
+      <c r="Y37" s="11" t="n"/>
+      <c r="Z37" s="8" t="n"/>
+      <c r="AA37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="11" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="11" t="n"/>
+      <c r="N38" s="8" t="n"/>
+      <c r="O38" s="11" t="n"/>
+      <c r="P38" s="8" t="n"/>
+      <c r="Q38" s="11" t="n"/>
+      <c r="R38" s="8" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="8" t="n"/>
+      <c r="U38" s="11" t="n"/>
+      <c r="V38" s="8" t="n"/>
+      <c r="W38" s="11" t="n"/>
+      <c r="X38" s="8" t="n"/>
+      <c r="Y38" s="11" t="n"/>
+      <c r="Z38" s="8" t="n"/>
+      <c r="AA38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="11" t="n"/>
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="11" t="n"/>
+      <c r="P39" s="8" t="n"/>
+      <c r="Q39" s="11" t="n"/>
+      <c r="R39" s="8" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="8" t="n"/>
+      <c r="U39" s="11" t="n"/>
+      <c r="V39" s="8" t="n"/>
+      <c r="W39" s="11" t="n"/>
+      <c r="X39" s="8" t="n"/>
+      <c r="Y39" s="11" t="n"/>
+      <c r="Z39" s="8" t="n"/>
+      <c r="AA39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="11" t="n"/>
+      <c r="N40" s="8" t="n"/>
+      <c r="O40" s="11" t="n"/>
+      <c r="P40" s="8" t="n"/>
+      <c r="Q40" s="11" t="n"/>
+      <c r="R40" s="8" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="8" t="n"/>
+      <c r="U40" s="11" t="n"/>
+      <c r="V40" s="8" t="n"/>
+      <c r="W40" s="11" t="n"/>
+      <c r="X40" s="8" t="n"/>
+      <c r="Y40" s="11" t="n"/>
+      <c r="Z40" s="8" t="n"/>
+      <c r="AA40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="8" t="n"/>
+      <c r="M41" s="11" t="n"/>
+      <c r="N41" s="8" t="n"/>
+      <c r="O41" s="11" t="n"/>
+      <c r="P41" s="8" t="n"/>
+      <c r="Q41" s="11" t="n"/>
+      <c r="R41" s="8" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="8" t="n"/>
+      <c r="U41" s="11" t="n"/>
+      <c r="V41" s="8" t="n"/>
+      <c r="W41" s="11" t="n"/>
+      <c r="X41" s="8" t="n"/>
+      <c r="Y41" s="11" t="n"/>
+      <c r="Z41" s="8" t="n"/>
+      <c r="AA41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="8" t="n"/>
+      <c r="M42" s="11" t="n"/>
+      <c r="N42" s="8" t="n"/>
+      <c r="O42" s="11" t="n"/>
+      <c r="P42" s="8" t="n"/>
+      <c r="Q42" s="11" t="n"/>
+      <c r="R42" s="8" t="n"/>
+      <c r="S42" s="11" t="n"/>
+      <c r="T42" s="8" t="n"/>
+      <c r="U42" s="11" t="n"/>
+      <c r="V42" s="8" t="n"/>
+      <c r="W42" s="11" t="n"/>
+      <c r="X42" s="8" t="n"/>
+      <c r="Y42" s="11" t="n"/>
+      <c r="Z42" s="8" t="n"/>
+      <c r="AA42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="11" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="11" t="n"/>
+      <c r="P43" s="8" t="n"/>
+      <c r="Q43" s="11" t="n"/>
+      <c r="R43" s="8" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="8" t="n"/>
+      <c r="U43" s="11" t="n"/>
+      <c r="V43" s="8" t="n"/>
+      <c r="W43" s="11" t="n"/>
+      <c r="X43" s="8" t="n"/>
+      <c r="Y43" s="11" t="n"/>
+      <c r="Z43" s="8" t="n"/>
+      <c r="AA43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="11" t="n"/>
+      <c r="L44" s="8" t="n"/>
+      <c r="M44" s="11" t="n"/>
+      <c r="N44" s="8" t="n"/>
+      <c r="O44" s="11" t="n"/>
+      <c r="P44" s="8" t="n"/>
+      <c r="Q44" s="11" t="n"/>
+      <c r="R44" s="8" t="n"/>
+      <c r="S44" s="11" t="n"/>
+      <c r="T44" s="8" t="n"/>
+      <c r="U44" s="11" t="n"/>
+      <c r="V44" s="8" t="n"/>
+      <c r="W44" s="11" t="n"/>
+      <c r="X44" s="8" t="n"/>
+      <c r="Y44" s="11" t="n"/>
+      <c r="Z44" s="8" t="n"/>
+      <c r="AA44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="8" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="8" t="n"/>
+      <c r="M45" s="11" t="n"/>
+      <c r="N45" s="8" t="n"/>
+      <c r="O45" s="11" t="n"/>
+      <c r="P45" s="8" t="n"/>
+      <c r="Q45" s="11" t="n"/>
+      <c r="R45" s="8" t="n"/>
+      <c r="S45" s="11" t="n"/>
+      <c r="T45" s="8" t="n"/>
+      <c r="U45" s="11" t="n"/>
+      <c r="V45" s="8" t="n"/>
+      <c r="W45" s="11" t="n"/>
+      <c r="X45" s="8" t="n"/>
+      <c r="Y45" s="11" t="n"/>
+      <c r="Z45" s="8" t="n"/>
+      <c r="AA45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="8" t="n"/>
+      <c r="K46" s="11" t="n"/>
+      <c r="L46" s="8" t="n"/>
+      <c r="M46" s="11" t="n"/>
+      <c r="N46" s="8" t="n"/>
+      <c r="O46" s="11" t="n"/>
+      <c r="P46" s="8" t="n"/>
+      <c r="Q46" s="11" t="n"/>
+      <c r="R46" s="8" t="n"/>
+      <c r="S46" s="11" t="n"/>
+      <c r="T46" s="8" t="n"/>
+      <c r="U46" s="11" t="n"/>
+      <c r="V46" s="8" t="n"/>
+      <c r="W46" s="11" t="n"/>
+      <c r="X46" s="8" t="n"/>
+      <c r="Y46" s="11" t="n"/>
+      <c r="Z46" s="8" t="n"/>
+      <c r="AA46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" s="8" t="n"/>
+      <c r="M47" s="11" t="n"/>
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="11" t="n"/>
+      <c r="P47" s="8" t="n"/>
+      <c r="Q47" s="11" t="n"/>
+      <c r="R47" s="8" t="n"/>
+      <c r="S47" s="11" t="n"/>
+      <c r="T47" s="8" t="n"/>
+      <c r="U47" s="11" t="n"/>
+      <c r="V47" s="8" t="n"/>
+      <c r="W47" s="11" t="n"/>
+      <c r="X47" s="8" t="n"/>
+      <c r="Y47" s="11" t="n"/>
+      <c r="Z47" s="8" t="n"/>
+      <c r="AA47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="8" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="11" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="11" t="n"/>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="11" t="n"/>
+      <c r="P48" s="8" t="n"/>
+      <c r="Q48" s="11" t="n"/>
+      <c r="R48" s="8" t="n"/>
+      <c r="S48" s="11" t="n"/>
+      <c r="T48" s="8" t="n"/>
+      <c r="U48" s="11" t="n"/>
+      <c r="V48" s="8" t="n"/>
+      <c r="W48" s="11" t="n"/>
+      <c r="X48" s="8" t="n"/>
+      <c r="Y48" s="11" t="n"/>
+      <c r="Z48" s="8" t="n"/>
+      <c r="AA48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="8" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="8" t="n"/>
+      <c r="M49" s="11" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="11" t="n"/>
+      <c r="P49" s="8" t="n"/>
+      <c r="Q49" s="11" t="n"/>
+      <c r="R49" s="8" t="n"/>
+      <c r="S49" s="11" t="n"/>
+      <c r="T49" s="8" t="n"/>
+      <c r="U49" s="11" t="n"/>
+      <c r="V49" s="8" t="n"/>
+      <c r="W49" s="11" t="n"/>
+      <c r="X49" s="8" t="n"/>
+      <c r="Y49" s="11" t="n"/>
+      <c r="Z49" s="8" t="n"/>
+      <c r="AA49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="8" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="11" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="11" t="n"/>
+      <c r="N50" s="8" t="n"/>
+      <c r="O50" s="11" t="n"/>
+      <c r="P50" s="8" t="n"/>
+      <c r="Q50" s="11" t="n"/>
+      <c r="R50" s="8" t="n"/>
+      <c r="S50" s="11" t="n"/>
+      <c r="T50" s="8" t="n"/>
+      <c r="U50" s="11" t="n"/>
+      <c r="V50" s="8" t="n"/>
+      <c r="W50" s="11" t="n"/>
+      <c r="X50" s="8" t="n"/>
+      <c r="Y50" s="11" t="n"/>
+      <c r="Z50" s="8" t="n"/>
+      <c r="AA50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="8" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="8" t="n"/>
+      <c r="M51" s="11" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="11" t="n"/>
+      <c r="P51" s="8" t="n"/>
+      <c r="Q51" s="11" t="n"/>
+      <c r="R51" s="8" t="n"/>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="8" t="n"/>
+      <c r="U51" s="11" t="n"/>
+      <c r="V51" s="8" t="n"/>
+      <c r="W51" s="11" t="n"/>
+      <c r="X51" s="8" t="n"/>
+      <c r="Y51" s="11" t="n"/>
+      <c r="Z51" s="8" t="n"/>
+      <c r="AA51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="11" t="n"/>
+      <c r="L52" s="8" t="n"/>
+      <c r="M52" s="11" t="n"/>
+      <c r="N52" s="8" t="n"/>
+      <c r="O52" s="11" t="n"/>
+      <c r="P52" s="8" t="n"/>
+      <c r="Q52" s="11" t="n"/>
+      <c r="R52" s="8" t="n"/>
+      <c r="S52" s="11" t="n"/>
+      <c r="T52" s="8" t="n"/>
+      <c r="U52" s="11" t="n"/>
+      <c r="V52" s="8" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="8" t="n"/>
+      <c r="Y52" s="11" t="n"/>
+      <c r="Z52" s="8" t="n"/>
+      <c r="AA52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="8" t="n"/>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="8" t="n"/>
+      <c r="M53" s="11" t="n"/>
+      <c r="N53" s="8" t="n"/>
+      <c r="O53" s="11" t="n"/>
+      <c r="P53" s="8" t="n"/>
+      <c r="Q53" s="11" t="n"/>
+      <c r="R53" s="8" t="n"/>
+      <c r="S53" s="11" t="n"/>
+      <c r="T53" s="8" t="n"/>
+      <c r="U53" s="11" t="n"/>
+      <c r="V53" s="8" t="n"/>
+      <c r="W53" s="11" t="n"/>
+      <c r="X53" s="8" t="n"/>
+      <c r="Y53" s="11" t="n"/>
+      <c r="Z53" s="8" t="n"/>
+      <c r="AA53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="8" t="n"/>
+      <c r="M54" s="11" t="n"/>
+      <c r="N54" s="8" t="n"/>
+      <c r="O54" s="11" t="n"/>
+      <c r="P54" s="8" t="n"/>
+      <c r="Q54" s="11" t="n"/>
+      <c r="R54" s="8" t="n"/>
+      <c r="S54" s="11" t="n"/>
+      <c r="T54" s="8" t="n"/>
+      <c r="U54" s="11" t="n"/>
+      <c r="V54" s="8" t="n"/>
+      <c r="W54" s="11" t="n"/>
+      <c r="X54" s="8" t="n"/>
+      <c r="Y54" s="11" t="n"/>
+      <c r="Z54" s="8" t="n"/>
+      <c r="AA54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="8" t="n"/>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="8" t="n"/>
+      <c r="M55" s="11" t="n"/>
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="11" t="n"/>
+      <c r="P55" s="8" t="n"/>
+      <c r="Q55" s="11" t="n"/>
+      <c r="R55" s="8" t="n"/>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="8" t="n"/>
+      <c r="U55" s="11" t="n"/>
+      <c r="V55" s="8" t="n"/>
+      <c r="W55" s="11" t="n"/>
+      <c r="X55" s="8" t="n"/>
+      <c r="Y55" s="11" t="n"/>
+      <c r="Z55" s="8" t="n"/>
+      <c r="AA55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="11" t="n"/>
+      <c r="J56" s="8" t="n"/>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="8" t="n"/>
+      <c r="M56" s="11" t="n"/>
+      <c r="N56" s="8" t="n"/>
+      <c r="O56" s="11" t="n"/>
+      <c r="P56" s="8" t="n"/>
+      <c r="Q56" s="11" t="n"/>
+      <c r="R56" s="8" t="n"/>
+      <c r="S56" s="11" t="n"/>
+      <c r="T56" s="8" t="n"/>
+      <c r="U56" s="11" t="n"/>
+      <c r="V56" s="8" t="n"/>
+      <c r="W56" s="11" t="n"/>
+      <c r="X56" s="8" t="n"/>
+      <c r="Y56" s="11" t="n"/>
+      <c r="Z56" s="8" t="n"/>
+      <c r="AA56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="11" t="n"/>
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="11" t="n"/>
+      <c r="J57" s="8" t="n"/>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="8" t="n"/>
+      <c r="M57" s="11" t="n"/>
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="11" t="n"/>
+      <c r="P57" s="8" t="n"/>
+      <c r="Q57" s="11" t="n"/>
+      <c r="R57" s="8" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="8" t="n"/>
+      <c r="U57" s="11" t="n"/>
+      <c r="V57" s="8" t="n"/>
+      <c r="W57" s="11" t="n"/>
+      <c r="X57" s="8" t="n"/>
+      <c r="Y57" s="11" t="n"/>
+      <c r="Z57" s="8" t="n"/>
+      <c r="AA57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="8" t="n"/>
+      <c r="M58" s="11" t="n"/>
+      <c r="N58" s="8" t="n"/>
+      <c r="O58" s="11" t="n"/>
+      <c r="P58" s="8" t="n"/>
+      <c r="Q58" s="11" t="n"/>
+      <c r="R58" s="8" t="n"/>
+      <c r="S58" s="11" t="n"/>
+      <c r="T58" s="8" t="n"/>
+      <c r="U58" s="11" t="n"/>
+      <c r="V58" s="8" t="n"/>
+      <c r="W58" s="11" t="n"/>
+      <c r="X58" s="8" t="n"/>
+      <c r="Y58" s="11" t="n"/>
+      <c r="Z58" s="8" t="n"/>
+      <c r="AA58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="8" t="n"/>
+      <c r="G59" s="11" t="n"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="8" t="n"/>
+      <c r="M59" s="11" t="n"/>
+      <c r="N59" s="8" t="n"/>
+      <c r="O59" s="11" t="n"/>
+      <c r="P59" s="8" t="n"/>
+      <c r="Q59" s="11" t="n"/>
+      <c r="R59" s="8" t="n"/>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="8" t="n"/>
+      <c r="U59" s="11" t="n"/>
+      <c r="V59" s="8" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="8" t="n"/>
+      <c r="Y59" s="11" t="n"/>
+      <c r="Z59" s="8" t="n"/>
+      <c r="AA59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="11" t="n"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="8" t="n"/>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="8" t="n"/>
+      <c r="M60" s="11" t="n"/>
+      <c r="N60" s="8" t="n"/>
+      <c r="O60" s="11" t="n"/>
+      <c r="P60" s="8" t="n"/>
+      <c r="Q60" s="11" t="n"/>
+      <c r="R60" s="8" t="n"/>
+      <c r="S60" s="11" t="n"/>
+      <c r="T60" s="8" t="n"/>
+      <c r="U60" s="11" t="n"/>
+      <c r="V60" s="8" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="8" t="n"/>
+      <c r="Y60" s="11" t="n"/>
+      <c r="Z60" s="8" t="n"/>
+      <c r="AA60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="8" t="n"/>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="8" t="n"/>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="8" t="n"/>
+      <c r="O61" s="11" t="n"/>
+      <c r="P61" s="8" t="n"/>
+      <c r="Q61" s="11" t="n"/>
+      <c r="R61" s="8" t="n"/>
+      <c r="S61" s="11" t="n"/>
+      <c r="T61" s="8" t="n"/>
+      <c r="U61" s="11" t="n"/>
+      <c r="V61" s="8" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="8" t="n"/>
+      <c r="Y61" s="11" t="n"/>
+      <c r="Z61" s="8" t="n"/>
+      <c r="AA61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="11" t="n"/>
+      <c r="N62" s="8" t="n"/>
+      <c r="O62" s="11" t="n"/>
+      <c r="P62" s="8" t="n"/>
+      <c r="Q62" s="11" t="n"/>
+      <c r="R62" s="8" t="n"/>
+      <c r="S62" s="11" t="n"/>
+      <c r="T62" s="8" t="n"/>
+      <c r="U62" s="11" t="n"/>
+      <c r="V62" s="8" t="n"/>
+      <c r="W62" s="11" t="n"/>
+      <c r="X62" s="8" t="n"/>
+      <c r="Y62" s="11" t="n"/>
+      <c r="Z62" s="8" t="n"/>
+      <c r="AA62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="8" t="n"/>
+      <c r="M63" s="11" t="n"/>
+      <c r="N63" s="8" t="n"/>
+      <c r="O63" s="11" t="n"/>
+      <c r="P63" s="8" t="n"/>
+      <c r="Q63" s="11" t="n"/>
+      <c r="R63" s="8" t="n"/>
+      <c r="S63" s="11" t="n"/>
+      <c r="T63" s="8" t="n"/>
+      <c r="U63" s="11" t="n"/>
+      <c r="V63" s="8" t="n"/>
+      <c r="W63" s="11" t="n"/>
+      <c r="X63" s="8" t="n"/>
+      <c r="Y63" s="11" t="n"/>
+      <c r="Z63" s="8" t="n"/>
+      <c r="AA63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="11" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="8" t="n"/>
+      <c r="M64" s="11" t="n"/>
+      <c r="N64" s="8" t="n"/>
+      <c r="O64" s="11" t="n"/>
+      <c r="P64" s="8" t="n"/>
+      <c r="Q64" s="11" t="n"/>
+      <c r="R64" s="8" t="n"/>
+      <c r="S64" s="11" t="n"/>
+      <c r="T64" s="8" t="n"/>
+      <c r="U64" s="11" t="n"/>
+      <c r="V64" s="8" t="n"/>
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="8" t="n"/>
+      <c r="Y64" s="11" t="n"/>
+      <c r="Z64" s="8" t="n"/>
+      <c r="AA64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n"/>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="8" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="8" t="n"/>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="8" t="n"/>
+      <c r="O65" s="11" t="n"/>
+      <c r="P65" s="8" t="n"/>
+      <c r="Q65" s="11" t="n"/>
+      <c r="R65" s="8" t="n"/>
+      <c r="S65" s="11" t="n"/>
+      <c r="T65" s="8" t="n"/>
+      <c r="U65" s="11" t="n"/>
+      <c r="V65" s="8" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="8" t="n"/>
+      <c r="Y65" s="11" t="n"/>
+      <c r="Z65" s="8" t="n"/>
+      <c r="AA65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="11" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="8" t="n"/>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="8" t="n"/>
+      <c r="M66" s="11" t="n"/>
+      <c r="N66" s="8" t="n"/>
+      <c r="O66" s="11" t="n"/>
+      <c r="P66" s="8" t="n"/>
+      <c r="Q66" s="11" t="n"/>
+      <c r="R66" s="8" t="n"/>
+      <c r="S66" s="11" t="n"/>
+      <c r="T66" s="8" t="n"/>
+      <c r="U66" s="11" t="n"/>
+      <c r="V66" s="8" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="8" t="n"/>
+      <c r="Y66" s="11" t="n"/>
+      <c r="Z66" s="8" t="n"/>
+      <c r="AA66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n"/>
+      <c r="B67" s="9" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="11" t="n"/>
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="8" t="n"/>
+      <c r="K67" s="11" t="n"/>
+      <c r="L67" s="8" t="n"/>
+      <c r="M67" s="11" t="n"/>
+      <c r="N67" s="8" t="n"/>
+      <c r="O67" s="11" t="n"/>
+      <c r="P67" s="8" t="n"/>
+      <c r="Q67" s="11" t="n"/>
+      <c r="R67" s="8" t="n"/>
+      <c r="S67" s="11" t="n"/>
+      <c r="T67" s="8" t="n"/>
+      <c r="U67" s="11" t="n"/>
+      <c r="V67" s="8" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="8" t="n"/>
+      <c r="Y67" s="11" t="n"/>
+      <c r="Z67" s="8" t="n"/>
+      <c r="AA67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="11" t="n"/>
+      <c r="N68" s="8" t="n"/>
+      <c r="O68" s="11" t="n"/>
+      <c r="P68" s="8" t="n"/>
+      <c r="Q68" s="11" t="n"/>
+      <c r="R68" s="8" t="n"/>
+      <c r="S68" s="11" t="n"/>
+      <c r="T68" s="8" t="n"/>
+      <c r="U68" s="11" t="n"/>
+      <c r="V68" s="8" t="n"/>
+      <c r="W68" s="11" t="n"/>
+      <c r="X68" s="8" t="n"/>
+      <c r="Y68" s="11" t="n"/>
+      <c r="Z68" s="8" t="n"/>
+      <c r="AA68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n"/>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="11" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="11" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="11" t="n"/>
+      <c r="N69" s="8" t="n"/>
+      <c r="O69" s="11" t="n"/>
+      <c r="P69" s="8" t="n"/>
+      <c r="Q69" s="11" t="n"/>
+      <c r="R69" s="8" t="n"/>
+      <c r="S69" s="11" t="n"/>
+      <c r="T69" s="8" t="n"/>
+      <c r="U69" s="11" t="n"/>
+      <c r="V69" s="8" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="8" t="n"/>
+      <c r="Y69" s="11" t="n"/>
+      <c r="Z69" s="8" t="n"/>
+      <c r="AA69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="8" t="n"/>
+      <c r="G70" s="11" t="n"/>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="11" t="n"/>
+      <c r="L70" s="8" t="n"/>
+      <c r="M70" s="11" t="n"/>
+      <c r="N70" s="8" t="n"/>
+      <c r="O70" s="11" t="n"/>
+      <c r="P70" s="8" t="n"/>
+      <c r="Q70" s="11" t="n"/>
+      <c r="R70" s="8" t="n"/>
+      <c r="S70" s="11" t="n"/>
+      <c r="T70" s="8" t="n"/>
+      <c r="U70" s="11" t="n"/>
+      <c r="V70" s="8" t="n"/>
+      <c r="W70" s="11" t="n"/>
+      <c r="X70" s="8" t="n"/>
+      <c r="Y70" s="11" t="n"/>
+      <c r="Z70" s="8" t="n"/>
+      <c r="AA70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n"/>
+      <c r="B71" s="9" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="11" t="n"/>
+      <c r="L71" s="8" t="n"/>
+      <c r="M71" s="11" t="n"/>
+      <c r="N71" s="8" t="n"/>
+      <c r="O71" s="11" t="n"/>
+      <c r="P71" s="8" t="n"/>
+      <c r="Q71" s="11" t="n"/>
+      <c r="R71" s="8" t="n"/>
+      <c r="S71" s="11" t="n"/>
+      <c r="T71" s="8" t="n"/>
+      <c r="U71" s="11" t="n"/>
+      <c r="V71" s="8" t="n"/>
+      <c r="W71" s="11" t="n"/>
+      <c r="X71" s="8" t="n"/>
+      <c r="Y71" s="11" t="n"/>
+      <c r="Z71" s="8" t="n"/>
+      <c r="AA71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="8" t="n"/>
+      <c r="G72" s="11" t="n"/>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="11" t="n"/>
+      <c r="L72" s="8" t="n"/>
+      <c r="M72" s="11" t="n"/>
+      <c r="N72" s="8" t="n"/>
+      <c r="O72" s="11" t="n"/>
+      <c r="P72" s="8" t="n"/>
+      <c r="Q72" s="11" t="n"/>
+      <c r="R72" s="8" t="n"/>
+      <c r="S72" s="11" t="n"/>
+      <c r="T72" s="8" t="n"/>
+      <c r="U72" s="11" t="n"/>
+      <c r="V72" s="8" t="n"/>
+      <c r="W72" s="11" t="n"/>
+      <c r="X72" s="8" t="n"/>
+      <c r="Y72" s="11" t="n"/>
+      <c r="Z72" s="8" t="n"/>
+      <c r="AA72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="11" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="11" t="n"/>
+      <c r="L73" s="8" t="n"/>
+      <c r="M73" s="11" t="n"/>
+      <c r="N73" s="8" t="n"/>
+      <c r="O73" s="11" t="n"/>
+      <c r="P73" s="8" t="n"/>
+      <c r="Q73" s="11" t="n"/>
+      <c r="R73" s="8" t="n"/>
+      <c r="S73" s="11" t="n"/>
+      <c r="T73" s="8" t="n"/>
+      <c r="U73" s="11" t="n"/>
+      <c r="V73" s="8" t="n"/>
+      <c r="W73" s="11" t="n"/>
+      <c r="X73" s="8" t="n"/>
+      <c r="Y73" s="11" t="n"/>
+      <c r="Z73" s="8" t="n"/>
+      <c r="AA73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n"/>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="11" t="n"/>
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="8" t="n"/>
+      <c r="K74" s="11" t="n"/>
+      <c r="L74" s="8" t="n"/>
+      <c r="M74" s="11" t="n"/>
+      <c r="N74" s="8" t="n"/>
+      <c r="O74" s="11" t="n"/>
+      <c r="P74" s="8" t="n"/>
+      <c r="Q74" s="11" t="n"/>
+      <c r="R74" s="8" t="n"/>
+      <c r="S74" s="11" t="n"/>
+      <c r="T74" s="8" t="n"/>
+      <c r="U74" s="11" t="n"/>
+      <c r="V74" s="8" t="n"/>
+      <c r="W74" s="11" t="n"/>
+      <c r="X74" s="8" t="n"/>
+      <c r="Y74" s="11" t="n"/>
+      <c r="Z74" s="8" t="n"/>
+      <c r="AA74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="8" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="8" t="n"/>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="8" t="n"/>
+      <c r="O75" s="11" t="n"/>
+      <c r="P75" s="8" t="n"/>
+      <c r="Q75" s="11" t="n"/>
+      <c r="R75" s="8" t="n"/>
+      <c r="S75" s="11" t="n"/>
+      <c r="T75" s="8" t="n"/>
+      <c r="U75" s="11" t="n"/>
+      <c r="V75" s="8" t="n"/>
+      <c r="W75" s="11" t="n"/>
+      <c r="X75" s="8" t="n"/>
+      <c r="Y75" s="11" t="n"/>
+      <c r="Z75" s="8" t="n"/>
+      <c r="AA75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="11" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="11" t="n"/>
+      <c r="L76" s="8" t="n"/>
+      <c r="M76" s="11" t="n"/>
+      <c r="N76" s="8" t="n"/>
+      <c r="O76" s="11" t="n"/>
+      <c r="P76" s="8" t="n"/>
+      <c r="Q76" s="11" t="n"/>
+      <c r="R76" s="8" t="n"/>
+      <c r="S76" s="11" t="n"/>
+      <c r="T76" s="8" t="n"/>
+      <c r="U76" s="11" t="n"/>
+      <c r="V76" s="8" t="n"/>
+      <c r="W76" s="11" t="n"/>
+      <c r="X76" s="8" t="n"/>
+      <c r="Y76" s="11" t="n"/>
+      <c r="Z76" s="8" t="n"/>
+      <c r="AA76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="11" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="11" t="n"/>
+      <c r="N77" s="8" t="n"/>
+      <c r="O77" s="11" t="n"/>
+      <c r="P77" s="8" t="n"/>
+      <c r="Q77" s="11" t="n"/>
+      <c r="R77" s="8" t="n"/>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="8" t="n"/>
+      <c r="U77" s="11" t="n"/>
+      <c r="V77" s="8" t="n"/>
+      <c r="W77" s="11" t="n"/>
+      <c r="X77" s="8" t="n"/>
+      <c r="Y77" s="11" t="n"/>
+      <c r="Z77" s="8" t="n"/>
+      <c r="AA77" s="8" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="8" t="n"/>
+      <c r="G78" s="11" t="n"/>
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="8" t="n"/>
+      <c r="M78" s="11" t="n"/>
+      <c r="N78" s="8" t="n"/>
+      <c r="O78" s="11" t="n"/>
+      <c r="P78" s="8" t="n"/>
+      <c r="Q78" s="11" t="n"/>
+      <c r="R78" s="8" t="n"/>
+      <c r="S78" s="11" t="n"/>
+      <c r="T78" s="8" t="n"/>
+      <c r="U78" s="11" t="n"/>
+      <c r="V78" s="8" t="n"/>
+      <c r="W78" s="11" t="n"/>
+      <c r="X78" s="8" t="n"/>
+      <c r="Y78" s="11" t="n"/>
+      <c r="Z78" s="8" t="n"/>
+      <c r="AA78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n"/>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="8" t="n"/>
+      <c r="G79" s="11" t="n"/>
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="8" t="n"/>
+      <c r="M79" s="11" t="n"/>
+      <c r="N79" s="8" t="n"/>
+      <c r="O79" s="11" t="n"/>
+      <c r="P79" s="8" t="n"/>
+      <c r="Q79" s="11" t="n"/>
+      <c r="R79" s="8" t="n"/>
+      <c r="S79" s="11" t="n"/>
+      <c r="T79" s="8" t="n"/>
+      <c r="U79" s="11" t="n"/>
+      <c r="V79" s="8" t="n"/>
+      <c r="W79" s="11" t="n"/>
+      <c r="X79" s="8" t="n"/>
+      <c r="Y79" s="11" t="n"/>
+      <c r="Z79" s="8" t="n"/>
+      <c r="AA79" s="8" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="8" t="n"/>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="8" t="n"/>
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="8" t="n"/>
+      <c r="O80" s="11" t="n"/>
+      <c r="P80" s="8" t="n"/>
+      <c r="Q80" s="11" t="n"/>
+      <c r="R80" s="8" t="n"/>
+      <c r="S80" s="11" t="n"/>
+      <c r="T80" s="8" t="n"/>
+      <c r="U80" s="11" t="n"/>
+      <c r="V80" s="8" t="n"/>
+      <c r="W80" s="11" t="n"/>
+      <c r="X80" s="8" t="n"/>
+      <c r="Y80" s="11" t="n"/>
+      <c r="Z80" s="8" t="n"/>
+      <c r="AA80" s="8" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n"/>
+      <c r="B81" s="9" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="11" t="n"/>
+      <c r="H81" s="8" t="n"/>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="8" t="n"/>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="8" t="n"/>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="8" t="n"/>
+      <c r="O81" s="11" t="n"/>
+      <c r="P81" s="8" t="n"/>
+      <c r="Q81" s="11" t="n"/>
+      <c r="R81" s="8" t="n"/>
+      <c r="S81" s="11" t="n"/>
+      <c r="T81" s="8" t="n"/>
+      <c r="U81" s="11" t="n"/>
+      <c r="V81" s="8" t="n"/>
+      <c r="W81" s="11" t="n"/>
+      <c r="X81" s="8" t="n"/>
+      <c r="Y81" s="11" t="n"/>
+      <c r="Z81" s="8" t="n"/>
+      <c r="AA81" s="8" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="8" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="8" t="n"/>
+      <c r="O82" s="11" t="n"/>
+      <c r="P82" s="8" t="n"/>
+      <c r="Q82" s="11" t="n"/>
+      <c r="R82" s="8" t="n"/>
+      <c r="S82" s="11" t="n"/>
+      <c r="T82" s="8" t="n"/>
+      <c r="U82" s="11" t="n"/>
+      <c r="V82" s="8" t="n"/>
+      <c r="W82" s="11" t="n"/>
+      <c r="X82" s="8" t="n"/>
+      <c r="Y82" s="11" t="n"/>
+      <c r="Z82" s="8" t="n"/>
+      <c r="AA82" s="8" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n"/>
+      <c r="B83" s="9" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="11" t="n"/>
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="11" t="n"/>
+      <c r="J83" s="8" t="n"/>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="8" t="n"/>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="8" t="n"/>
+      <c r="O83" s="11" t="n"/>
+      <c r="P83" s="8" t="n"/>
+      <c r="Q83" s="11" t="n"/>
+      <c r="R83" s="8" t="n"/>
+      <c r="S83" s="11" t="n"/>
+      <c r="T83" s="8" t="n"/>
+      <c r="U83" s="11" t="n"/>
+      <c r="V83" s="8" t="n"/>
+      <c r="W83" s="11" t="n"/>
+      <c r="X83" s="8" t="n"/>
+      <c r="Y83" s="11" t="n"/>
+      <c r="Z83" s="8" t="n"/>
+      <c r="AA83" s="8" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="8" t="n"/>
+      <c r="K84" s="11" t="n"/>
+      <c r="L84" s="8" t="n"/>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="8" t="n"/>
+      <c r="O84" s="11" t="n"/>
+      <c r="P84" s="8" t="n"/>
+      <c r="Q84" s="11" t="n"/>
+      <c r="R84" s="8" t="n"/>
+      <c r="S84" s="11" t="n"/>
+      <c r="T84" s="8" t="n"/>
+      <c r="U84" s="11" t="n"/>
+      <c r="V84" s="8" t="n"/>
+      <c r="W84" s="11" t="n"/>
+      <c r="X84" s="8" t="n"/>
+      <c r="Y84" s="11" t="n"/>
+      <c r="Z84" s="8" t="n"/>
+      <c r="AA84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="n"/>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="11" t="n"/>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="11" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="11" t="n"/>
+      <c r="L85" s="8" t="n"/>
+      <c r="M85" s="11" t="n"/>
+      <c r="N85" s="8" t="n"/>
+      <c r="O85" s="11" t="n"/>
+      <c r="P85" s="8" t="n"/>
+      <c r="Q85" s="11" t="n"/>
+      <c r="R85" s="8" t="n"/>
+      <c r="S85" s="11" t="n"/>
+      <c r="T85" s="8" t="n"/>
+      <c r="U85" s="11" t="n"/>
+      <c r="V85" s="8" t="n"/>
+      <c r="W85" s="11" t="n"/>
+      <c r="X85" s="8" t="n"/>
+      <c r="Y85" s="11" t="n"/>
+      <c r="Z85" s="8" t="n"/>
+      <c r="AA85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="11" t="n"/>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="11" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="11" t="n"/>
+      <c r="L86" s="8" t="n"/>
+      <c r="M86" s="11" t="n"/>
+      <c r="N86" s="8" t="n"/>
+      <c r="O86" s="11" t="n"/>
+      <c r="P86" s="8" t="n"/>
+      <c r="Q86" s="11" t="n"/>
+      <c r="R86" s="8" t="n"/>
+      <c r="S86" s="11" t="n"/>
+      <c r="T86" s="8" t="n"/>
+      <c r="U86" s="11" t="n"/>
+      <c r="V86" s="8" t="n"/>
+      <c r="W86" s="11" t="n"/>
+      <c r="X86" s="8" t="n"/>
+      <c r="Y86" s="11" t="n"/>
+      <c r="Z86" s="8" t="n"/>
+      <c r="AA86" s="8" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="1" sort="1" password="D8C7"/>
   <mergeCells count="5">
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A5:Y5"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A4:Y4"/>
-    <mergeCell ref="A3:Y3"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="B1:AA1"/>
+    <mergeCell ref="B2:AA2"/>
+    <mergeCell ref="A5:AA5"/>
+    <mergeCell ref="B3:AA3"/>
   </mergeCells>
+  <conditionalFormatting sqref="F7:F86">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G86">
+    <cfRule type="expression" priority="4" dxfId="1">
+      <formula>AND(G7&lt;&gt;"",G7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>AND(G7&lt;&gt;"",G7&gt;=TODAY(),G7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H7:H86">
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I7:I86">
+    <cfRule type="expression" priority="9" dxfId="1">
+      <formula>AND(I7&lt;&gt;"",I7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="3">
+      <formula>AND(I7&lt;&gt;"",I7&gt;=TODAY(),I7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7:J86">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K7:K86">
+    <cfRule type="expression" priority="14" dxfId="1">
+      <formula>AND(K7&lt;&gt;"",K7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="3">
+      <formula>AND(K7&lt;&gt;"",K7&gt;=TODAY(),K7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L7:L86">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="17" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M7:M86">
+    <cfRule type="expression" priority="19" dxfId="1">
+      <formula>AND(M7&lt;&gt;"",M7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="3">
+      <formula>AND(M7&lt;&gt;"",M7&gt;=TODAY(),M7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N86">
+    <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="22" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:O86">
+    <cfRule type="expression" priority="24" dxfId="1">
+      <formula>AND(O7&lt;&gt;"",O7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="25" dxfId="3">
+      <formula>AND(O7&lt;&gt;"",O7&gt;=TODAY(),O7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P7:P86">
+    <cfRule type="cellIs" priority="26" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="27" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="28" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7:Q86">
+    <cfRule type="expression" priority="29" dxfId="1">
+      <formula>AND(Q7&lt;&gt;"",Q7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="3">
+      <formula>AND(Q7&lt;&gt;"",Q7&gt;=TODAY(),Q7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R7:R86">
+    <cfRule type="cellIs" priority="31" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S7:S86">
+    <cfRule type="expression" priority="34" dxfId="1">
+      <formula>AND(S7&lt;&gt;"",S7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="3">
+      <formula>AND(S7&lt;&gt;"",S7&gt;=TODAY(),S7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T7:T86">
+    <cfRule type="cellIs" priority="36" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="37" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="38" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U7:U86">
+    <cfRule type="expression" priority="39" dxfId="1">
+      <formula>AND(U7&lt;&gt;"",U7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="40" dxfId="3">
+      <formula>AND(U7&lt;&gt;"",U7&gt;=TODAY(),U7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V86">
+    <cfRule type="cellIs" priority="41" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="43" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W7:W86">
+    <cfRule type="expression" priority="44" dxfId="1">
+      <formula>AND(W7&lt;&gt;"",W7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="45" dxfId="3">
+      <formula>AND(W7&lt;&gt;"",W7&gt;=TODAY(),W7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X7:X86">
+    <cfRule type="cellIs" priority="46" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="47" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="48" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y86">
+    <cfRule type="expression" priority="49" dxfId="1">
+      <formula>AND(Y7&lt;&gt;"",Y7&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" priority="50" dxfId="3">
+      <formula>AND(Y7&lt;&gt;"",Y7&gt;=TODAY(),Y7&lt;=TODAY()+30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z7:Z86">
+    <cfRule type="cellIs" priority="51" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="52" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="53" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA86">
+    <cfRule type="cellIs" priority="54" operator="equal" dxfId="0">
+      <formula>"Apto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="55" operator="equal" dxfId="1">
+      <formula>"Inapto"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="56" operator="equal" dxfId="2">
+      <formula>"Não se aplica"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="23">
+    <dataValidation sqref="E7:E86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Digite um número." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="F7:F86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="ASO: status do documento. Atestado de Saúde Ocupacional. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G7:G86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="H7:H86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-06: status do documento. EPI. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I7:I86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="J7:J86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-10: status do documento. Eletricidade. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K7:K86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="L7:L86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-11: status do documento. Cargas. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M7:M86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="N7:N86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-12: status do documento. Máquinas. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O7:O86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="P7:P86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-18: status do documento. Construção civil. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q7:Q86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="R7:R86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-20: status do documento. Inflamáveis. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S7:S86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="T7:T86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-23: status do documento. Incêndio. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U7:U86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="V7:V86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-33: status do documento. Espaço confinado. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="W7:W86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="X7:X86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="NR-35: status do documento. Altura. Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y7:Y86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Data inválida." type="date" operator="greaterThan">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z7:Z86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="Integração junto à CORSAN: Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA7:AA86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." prompt="Situação no SERTRAS: Apto / Inapto / Não se aplica." type="list">
+      <formula1>"Apto,Inapto,Não se aplica"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B4:B43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="38" customHeight="1"/>
+    <row r="4">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>GRAVITAS · PAINEL DE CONTROLE — Funcionários</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>• Não altere as linhas de cabeçalho/instruções (1 a 6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>• Preencha só as células em AMARELO CLARO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>• Onde houver lista (▾), escolha um valor — não digite à mão.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>• Datas no formato DD/MM/AAAA. Decimais com vírgula. Ano = número inteiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>• Status de documento: Apto / Inapto / Não se aplica (ou deixe em branco).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Colunas:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Observações:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>• NOVO: colunas 'Integração CORSAN' e 'SERTRAS' (status Apto/Inapto/Não se aplica) — o importador deve lê-las.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>• Status mapeado: Apto=1, Inapto=2, Não se aplica=3; em branco = não informado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>•  Nome Completo: Nome completo do funcionário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>•  CPF (somente números): CPF só números, 11 dígitos (ex.: 12345678901).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>•  Empresa: Empresa empregadora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>•  Função: Cargo/função na obra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>•  Salário: Salário base mensal (R$).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>•  ASO: ASO: status do documento. Atestado de Saúde Ocupacional. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade ASO: Validade do ASO (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-06: NR-06: status do documento. EPI. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-06: Validade do NR-06 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-10: NR-10: status do documento. Eletricidade. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-10: Validade do NR-10 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-11: NR-11: status do documento. Cargas. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-11: Validade do NR-11 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-12: NR-12: status do documento. Máquinas. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-12: Validade do NR-12 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-18: NR-18: status do documento. Construção civil. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-18: Validade do NR-18 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-20: NR-20: status do documento. Inflamáveis. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-20: Validade do NR-20 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-23: NR-23: status do documento. Incêndio. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-23: Validade do NR-23 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-33: NR-33: status do documento. Espaço confinado. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-33: Validade do NR-33 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>•  NR-35: NR-35: status do documento. Altura. Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>•  Validade NR-35: Validade do NR-35 (DD/MM/AAAA). Vermelho=vencido; âmbar=vence em 30 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>•  Integração CORSAN: Integração junto à CORSAN: Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>•  SERTRAS: Situação no SERTRAS: Apto / Inapto / Não se aplica.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="D8C7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>